--- a/00_NA_Status_All_Accounts_11-Jun-2026.xlsx
+++ b/00_NA_Status_All_Accounts_11-Jun-2026.xlsx
@@ -464,7 +464,7 @@
     <t xml:space="preserve">Management Consultancies</t>
   </si>
   <si>
-    <t xml:space="preserve">Full account parsed, 9 lines $46,003.66, reconciles to SE2 exact. Single engagement: Organisational Risk Consulting Pty Ltd, Parks Branch WHS Gap Analysis (Consultancy Agreement, T&amp;M, consultant Andrea Paynter, PO 711200/712924). 1 of 9 invoices sighted: INV-251010(2) $2,132.63 via GJ078546, GST $213.26 exact, $2,345.89 incl = GL x 1.1 exact; consultancy four-element test met on the face; 73601 correct. Invoice addressee corroborates Anita Moore as Acting Parks Manager (bears on her home-service...</t>
+    <t xml:space="preserve">Full account parsed, 9 lines $46,003.66, reconciles to SE2 exact. Single engagement: Organisational Risk Consulting Pty Ltd, Parks Branch WHS Gap Analysis (Consultancy Agreement, T&amp;M, consultant Andrea Paynter, PO 711200/712924). 1 of 9 invoices sighted: INV-251010(2) $2,132.63 via GJ078546, GST $213.26 exact, $2,345.89 incl = GL x 1.1 exact; consultancy four-element test met on the face; 73601 correct. Invoice addressee corroborates Anita Moore as Acting Parks Manager (bears on her home-service... EVIDENCE CLOSED 16-Jun: 8 Org Risk Consulting invoices sighted ($43,871.03 exact), 9 of 9, all A</t>
   </si>
   <si>
     <t xml:space="preserve">1 Obtain the 8 Org Risk invoices ($43,871.03). 2 Run ABR/ASIC dossier on ABN 27 651 588 662 when the set lands. 3 Check engagement period vs the 12-month contractor cap (runs 30-Jul-2025 onward on sighted docs).</t>
@@ -2516,13 +2516,13 @@
     <row r="9" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="14" t="n">
         <f aca="false">COUNTIF('All Accounts'!G5:G91,"Fully reviewed")</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C9" s="14"/>
       <c r="D9" s="14"/>
       <c r="E9" s="15" t="n">
         <f aca="false">COUNTIF('All Accounts'!G5:G91,"Partial")</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F9" s="15"/>
       <c r="G9" s="15"/>
@@ -2581,13 +2581,13 @@
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="23" t="n">
         <f aca="false">COUNTIF('All Accounts'!N5:N91,"GREEN")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" s="23"/>
       <c r="D13" s="23"/>
       <c r="E13" s="24" t="n">
         <f aca="false">COUNTIF('All Accounts'!N5:N91,"AMBER")</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F13" s="24"/>
       <c r="G13" s="24"/>
@@ -2808,7 +2808,7 @@
         <v>538947.73</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="31" t="s">
         <v>32</v>
       </c>
@@ -3971,7 +3971,7 @@
         <v>57</v>
       </c>
       <c r="G26" s="39" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="H26" s="41" t="n">
         <v>46003.66</v>
@@ -3986,13 +3986,13 @@
         <v>11</v>
       </c>
       <c r="L26" s="42" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M26" s="42" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N26" s="42" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O26" s="40" t="s">
         <v>145</v>
